--- a/practice_test/real_document/generated/PRJ-9201_tender_pack_r1/PRJ-9201-D10_r1_Commercial-clarifications.xlsx
+++ b/practice_test/real_document/generated/PRJ-9201_tender_pack_r1/PRJ-9201-D10_r1_Commercial-clarifications.xlsx
@@ -682,7 +682,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TQ-PRJ-9201-027</t>
+          <t>TQ-PRJ-9201-031</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TQ-PRJ-9201-028</t>
+          <t>TQ-PRJ-9201-032</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -744,7 +744,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TQ-PRJ-9201-029</t>
+          <t>TQ-PRJ-9201-033</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -775,7 +775,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TQ-PRJ-9201-036</t>
+          <t>TQ-PRJ-9201-040</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
